--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISCO D\Francisco\Trabajos\FCE\Optativa\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0587CA0E-AC2D-4C9E-A430-4114A4495A75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EF60DB-3F9A-46EC-BEAD-D91B0FCA57FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -423,167 +420,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -900,7 +737,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="21">
-        <v>45903.989892245372</v>
+        <v>45909.466932870368</v>
       </c>
       <c r="E3" s="22"/>
       <c r="H3" s="12"/>
@@ -986,7 +823,9 @@
       <c r="E8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="10"/>
+      <c r="F8" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
       <c r="I8" s="10"/>
@@ -1342,93 +1181,13 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:K16 F18:K18">
-    <cfRule type="cellIs" dxfId="17" priority="18" operator="equal">
+  <conditionalFormatting sqref="D8:K27">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" dxfId="16" priority="17" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D17:K17">
-    <cfRule type="cellIs" dxfId="15" priority="16" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D19:K19">
-    <cfRule type="cellIs" dxfId="14" priority="15" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D20:K20">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D21:K21">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D22:K22">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23:K23">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:K24">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F25:K25">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26:K26">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23:E23">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D24:E24">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:E18">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F27:K27">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D27:E27">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D26:E26">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D25:E25">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISCO D\Francisco\Trabajos\FCE\Optativa\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EF60DB-3F9A-46EC-BEAD-D91B0FCA57FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213E9965-B45A-45E6-A5D2-47A4D005B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -96,9 +99,6 @@
     <t>Bressan, Diane</t>
   </si>
   <si>
-    <t>Bona, Leandro Nahuel</t>
-  </si>
-  <si>
     <t>Pereyra, Franco Andrés</t>
   </si>
   <si>
@@ -121,6 +121,9 @@
   </si>
   <si>
     <t>Pontelli, Lara</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>
@@ -717,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N27"/>
+  <dimension ref="B2:N26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -737,7 +740,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="21">
-        <v>45909.466932870368</v>
+        <v>45910.900046296294</v>
       </c>
       <c r="E3" s="22"/>
       <c r="H3" s="12"/>
@@ -814,14 +817,14 @@
     </row>
     <row r="8" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>5</v>
@@ -834,16 +837,18 @@
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
       <c r="I9" s="10"/>
@@ -852,16 +857,18 @@
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="10"/>
+        <v>28</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
       <c r="I10" s="10"/>
@@ -870,16 +877,18 @@
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
       <c r="I11" s="10"/>
@@ -888,16 +897,18 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="10"/>
+        <v>14</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
@@ -906,16 +917,18 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
       <c r="I13" s="10"/>
@@ -924,7 +937,7 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="10" t="s">
@@ -942,16 +955,18 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F15" s="10"/>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
       <c r="I15" s="10"/>
@@ -960,14 +975,14 @@
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F16" s="10"/>
       <c r="G16" s="10"/>
@@ -978,16 +993,18 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" s="10"/>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
       <c r="I17" s="10"/>
@@ -996,16 +1013,18 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" s="10"/>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
@@ -1014,16 +1033,18 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" s="10"/>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
@@ -1032,14 +1053,14 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="10"/>
@@ -1050,16 +1071,18 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
@@ -1068,14 +1091,14 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -1086,16 +1109,18 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
@@ -1104,16 +1129,18 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="10"/>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
@@ -1122,16 +1149,18 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="10"/>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
@@ -1140,14 +1169,14 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1156,32 +1185,17 @@
       <c r="J26" s="10"/>
       <c r="K26" s="11"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="11"/>
-    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:K26">
+    <sortCondition ref="B8:B26"/>
+  </sortState>
   <mergeCells count="4">
     <mergeCell ref="D6:K6"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:K27">
+  <conditionalFormatting sqref="D8:K26">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213E9965-B45A-45E6-A5D2-47A4D005B8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390B6737-6BFF-4FCE-B7CE-54E970C3E4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -740,7 +740,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="21">
-        <v>45910.900046296294</v>
+        <v>45910.980636574073</v>
       </c>
       <c r="E3" s="22"/>
       <c r="H3" s="12"/>
@@ -827,7 +827,7 @@
         <v>28</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -867,7 +867,7 @@
         <v>28</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -887,7 +887,7 @@
         <v>13</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -907,7 +907,7 @@
         <v>14</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -927,7 +927,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
@@ -965,7 +965,7 @@
         <v>13</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -1003,7 +1003,7 @@
         <v>13</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -1023,7 +1023,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -1043,7 +1043,7 @@
         <v>13</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -1062,7 +1062,9 @@
       <c r="E20" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F20" s="10"/>
+      <c r="F20" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
@@ -1100,7 +1102,9 @@
       <c r="E22" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="10"/>
+      <c r="F22" s="10" t="s">
+        <v>14</v>
+      </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
@@ -1119,7 +1123,7 @@
         <v>13</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -1139,7 +1143,7 @@
         <v>14</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1159,7 +1163,7 @@
         <v>13</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISCO D\Francisco\Trabajos\FCE\Optativa\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{390B6737-6BFF-4FCE-B7CE-54E970C3E4E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071650D5-CC18-4081-BECD-5152909427D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="28">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -64,9 +61,6 @@
   </si>
   <si>
     <t>Referencias</t>
-  </si>
-  <si>
-    <t>Enviado fuera de término</t>
   </si>
   <si>
     <t>Recibido (sin calificar aún)</t>
@@ -130,7 +124,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -138,8 +132,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,14 +154,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="20">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -321,24 +317,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -368,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -385,13 +363,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -418,6 +394,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,61 +706,53 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="23"/>
     </row>
     <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="21">
-        <v>45910.980636574073</v>
-      </c>
-      <c r="E3" s="22"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="5" t="s">
+      <c r="D3" s="19">
+        <v>45911.541770833333</v>
+      </c>
+      <c r="E3" s="20"/>
+      <c r="H3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="H4" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="J4" s="15"/>
-      <c r="K4" s="16"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="14"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="18"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="20"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="7"/>
       <c r="D7" s="8">
         <v>45894</v>
@@ -821,13 +792,13 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" s="10"/>
       <c r="H8" s="10"/>
@@ -837,17 +808,17 @@
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" s="10"/>
       <c r="H9" s="10"/>
@@ -857,17 +828,17 @@
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
@@ -881,13 +852,13 @@
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10"/>
@@ -897,17 +868,17 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -917,17 +888,17 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
@@ -937,14 +908,14 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -955,17 +926,17 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
@@ -979,12 +950,14 @@
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>5</v>
+      </c>
       <c r="G16" s="10"/>
       <c r="H16" s="10"/>
       <c r="I16" s="10"/>
@@ -997,13 +970,13 @@
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="10"/>
@@ -1013,17 +986,17 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -1033,17 +1006,17 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -1053,17 +1026,17 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -1073,17 +1046,17 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -1093,17 +1066,17 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -1113,17 +1086,17 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -1133,17 +1106,17 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" s="10"/>
       <c r="H24" s="10"/>
@@ -1153,17 +1126,17 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" s="10"/>
       <c r="H25" s="10"/>
@@ -1173,14 +1146,14 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -1204,7 +1177,7 @@
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4">
+  <conditionalFormatting sqref="H3">
     <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
       <formula>"R"</formula>
     </cfRule>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISCO D\Francisco\Trabajos\FCE\Optativa\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{071650D5-CC18-4081-BECD-5152909427D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380E0F11-281D-4492-B12F-28DE2B394E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,12 +29,162 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Francisco Leiva</author>
+  </authors>
+  <commentList>
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{06101C33-265A-46BE-A734-9895C84C80F6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Error: objeto 'tab' no encontrado
+Error: objeto 'mean_by_month' no encontrado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{BAC2716D-1FF6-4460-89A0-0563EA2A9792}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Error: `path` does not exist: ‘Growth.xlsx’</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{452042C0-E791-466A-BF82-179BD80140AB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Error: `path` does not exist: ‘Growth.xlsx’</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{3254A794-DC4A-404E-831A-F9197FDD3E71}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No corrió bien el codigo</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{CEEDE685-C6D5-416F-82DE-962D277B8B88}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+Error: objeto 'ventas_autos_caba' no encontrado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{63CC2A39-887A-4ED0-A3CF-879F00553721}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+Error en file(file, "rt"): no se puede abrir la conexión
+Además: Aviso:
+In file(file, "rt") :
+  no fue posible abrir el archivo 'datos_wdi.csv': No such file or directory</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{7B08EDC2-9450-4D0E-BC3E-679B5C0F8CE2}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Error en drop_na(., Ozone, Temp): 
+  no se pudo encontrar la función "drop_na"</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{FABC9E6E-5273-4913-8085-012620829B29}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+Error: `path` does not exist: ‘encuesta_poblacional.xlsx’</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{C8160E2B-76BE-4EC9-B84F-541AF26D2261}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Error en file(file, "rt"): no se puede abrir la conexión
+Además: Aviso:
+In file(file, "rt") :
+  no fue posible abrir el archivo '…/Programacion en R/base.csv': No such file or directory</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -118,13 +268,16 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>Gallucio, Tomas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,8 +293,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -154,6 +314,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="18">
     <border>
@@ -346,7 +512,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -368,6 +534,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -395,7 +564,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -698,30 +867,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:N27"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="21" t="s">
+      <c r="H2" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
     </row>
     <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="19">
-        <v>45911.541770833333</v>
-      </c>
-      <c r="E3" s="20"/>
+      <c r="D3" s="20">
+        <v>45942.525694444441</v>
+      </c>
+      <c r="E3" s="21"/>
       <c r="H3" s="12" t="s">
         <v>5</v>
       </c>
@@ -733,26 +902,26 @@
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="17"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="18"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="7"/>
       <c r="D7" s="8">
         <v>45894</v>
@@ -800,9 +969,13 @@
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>27</v>
+      </c>
       <c r="J8" s="10"/>
       <c r="K8" s="11"/>
     </row>
@@ -820,9 +993,13 @@
       <c r="F9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="J9" s="10"/>
       <c r="K9" s="11"/>
     </row>
@@ -840,8 +1017,10 @@
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I10" s="10"/>
       <c r="J10" s="10"/>
       <c r="K10" s="11"/>
@@ -860,27 +1039,31 @@
       <c r="F11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="J11" s="10"/>
       <c r="K11" s="11"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="6" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="10"/>
+      <c r="D12" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G12" s="25"/>
       <c r="H12" s="10"/>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
@@ -888,37 +1071,41 @@
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="G13" s="25"/>
+      <c r="H13" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I13" s="10"/>
       <c r="J13" s="10"/>
       <c r="K13" s="11"/>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G14" s="25"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
@@ -926,67 +1113,75 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G15" s="25"/>
+      <c r="H15" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I15" s="10"/>
       <c r="J15" s="10"/>
       <c r="K15" s="11"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="25"/>
+      <c r="H16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="J16" s="10"/>
       <c r="K16" s="11"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G17" s="25"/>
+      <c r="H17" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="I17" s="10"/>
       <c r="J17" s="10"/>
       <c r="K17" s="11"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="10" t="s">
@@ -998,19 +1193,21 @@
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I18" s="10"/>
       <c r="J18" s="10"/>
       <c r="K18" s="11"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>12</v>
@@ -1018,153 +1215,193 @@
       <c r="F19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="I19" s="10"/>
       <c r="J19" s="10"/>
       <c r="K19" s="11"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I20" s="10"/>
       <c r="J20" s="10"/>
       <c r="K20" s="11"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
+        <v>13</v>
+      </c>
+      <c r="G21" s="25"/>
+      <c r="H21" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I21" s="10"/>
       <c r="J21" s="10"/>
       <c r="K21" s="11"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
+        <v>12</v>
+      </c>
+      <c r="G22" s="25"/>
+      <c r="H22" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I22" s="10"/>
       <c r="J22" s="10"/>
       <c r="K22" s="11"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="10" t="s">
+        <v>5</v>
+      </c>
       <c r="I23" s="10"/>
       <c r="J23" s="10"/>
       <c r="K23" s="11"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I24" s="10"/>
       <c r="J24" s="10"/>
       <c r="K24" s="11"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I25" s="10"/>
       <c r="J25" s="10"/>
       <c r="K25" s="11"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E26" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
+      <c r="F26" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" s="25"/>
+      <c r="H26" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I26" s="10"/>
       <c r="J26" s="10"/>
       <c r="K26" s="11"/>
     </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="25"/>
+      <c r="H27" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+      <c r="K27" s="11"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:K26">
-    <sortCondition ref="B8:B26"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:K27">
+    <sortCondition ref="B8:B27"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="D6:K6"/>
@@ -1172,7 +1409,7 @@
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:K26">
+  <conditionalFormatting sqref="D8:K27">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
@@ -1183,5 +1420,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{380E0F11-281D-4492-B12F-28DE2B394E60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B1CF9D-AE2D-4F98-B7E3-13ED4A3EAFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -537,6 +537,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -563,9 +566,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -875,22 +875,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="20">
+      <c r="D3" s="21">
         <v>45942.525694444441</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="E3" s="22"/>
       <c r="H3" s="12" t="s">
         <v>5</v>
       </c>
@@ -902,26 +902,26 @@
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
-      <c r="K6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="19"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="7"/>
       <c r="D7" s="8">
         <v>45894</v>
@@ -969,7 +969,7 @@
       <c r="F8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="16"/>
       <c r="H8" s="15" t="s">
         <v>13</v>
       </c>
@@ -993,7 +993,7 @@
       <c r="F9" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="16"/>
       <c r="H9" s="10" t="s">
         <v>13</v>
       </c>
@@ -1017,7 +1017,7 @@
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="25"/>
+      <c r="G10" s="16"/>
       <c r="H10" s="10" t="s">
         <v>13</v>
       </c>
@@ -1039,7 +1039,7 @@
       <c r="F11" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="16"/>
       <c r="H11" s="10" t="s">
         <v>5</v>
       </c>
@@ -1063,8 +1063,10 @@
       <c r="F12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="25"/>
-      <c r="H12" s="10"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="I12" s="10"/>
       <c r="J12" s="10"/>
       <c r="K12" s="11"/>
@@ -1083,7 +1085,7 @@
       <c r="F13" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="16"/>
       <c r="H13" s="10" t="s">
         <v>13</v>
       </c>
@@ -1105,7 +1107,7 @@
       <c r="F14" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="25"/>
+      <c r="G14" s="16"/>
       <c r="H14" s="10"/>
       <c r="I14" s="10"/>
       <c r="J14" s="10"/>
@@ -1125,7 +1127,7 @@
       <c r="F15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="25"/>
+      <c r="G15" s="16"/>
       <c r="H15" s="10" t="s">
         <v>13</v>
       </c>
@@ -1147,7 +1149,7 @@
       <c r="F16" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="16"/>
       <c r="H16" s="10" t="s">
         <v>12</v>
       </c>
@@ -1171,7 +1173,7 @@
       <c r="F17" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="16"/>
       <c r="H17" s="10" t="s">
         <v>5</v>
       </c>
@@ -1193,7 +1195,7 @@
       <c r="F18" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="25"/>
+      <c r="G18" s="16"/>
       <c r="H18" s="10" t="s">
         <v>13</v>
       </c>
@@ -1215,7 +1217,7 @@
       <c r="F19" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="25"/>
+      <c r="G19" s="16"/>
       <c r="H19" s="10" t="s">
         <v>5</v>
       </c>
@@ -1237,7 +1239,7 @@
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="25"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="10" t="s">
         <v>13</v>
       </c>
@@ -1259,7 +1261,7 @@
       <c r="F21" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="25"/>
+      <c r="G21" s="16"/>
       <c r="H21" s="10" t="s">
         <v>13</v>
       </c>
@@ -1281,7 +1283,7 @@
       <c r="F22" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="25"/>
+      <c r="G22" s="16"/>
       <c r="H22" s="10" t="s">
         <v>13</v>
       </c>
@@ -1303,7 +1305,7 @@
       <c r="F23" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="25"/>
+      <c r="G23" s="16"/>
       <c r="H23" s="10" t="s">
         <v>5</v>
       </c>
@@ -1325,7 +1327,7 @@
       <c r="F24" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="25"/>
+      <c r="G24" s="16"/>
       <c r="H24" s="10" t="s">
         <v>13</v>
       </c>
@@ -1347,7 +1349,7 @@
       <c r="F25" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="25"/>
+      <c r="G25" s="16"/>
       <c r="H25" s="10" t="s">
         <v>13</v>
       </c>
@@ -1369,7 +1371,7 @@
       <c r="F26" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="25"/>
+      <c r="G26" s="16"/>
       <c r="H26" s="10" t="s">
         <v>13</v>
       </c>
@@ -1391,7 +1393,7 @@
       <c r="F27" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="25"/>
+      <c r="G27" s="16"/>
       <c r="H27" s="15" t="s">
         <v>5</v>
       </c>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B1CF9D-AE2D-4F98-B7E3-13ED4A3EAFE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F661FB-276D-4E08-9186-57195F1AB6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
     <author>Francisco Leiva</author>
   </authors>
   <commentList>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{06101C33-265A-46BE-A734-9895C84C80F6}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{06101C33-265A-46BE-A734-9895C84C80F6}">
       <text>
         <r>
           <rPr>
@@ -57,7 +57,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{BAC2716D-1FF6-4460-89A0-0563EA2A9792}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{BAC2716D-1FF6-4460-89A0-0563EA2A9792}">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{452042C0-E791-466A-BF82-179BD80140AB}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{452042C0-E791-466A-BF82-179BD80140AB}">
       <text>
         <r>
           <rPr>
@@ -85,7 +85,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{3254A794-DC4A-404E-831A-F9197FDD3E71}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{3254A794-DC4A-404E-831A-F9197FDD3E71}">
       <text>
         <r>
           <rPr>
@@ -99,7 +99,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{CEEDE685-C6D5-416F-82DE-962D277B8B88}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{CEEDE685-C6D5-416F-82DE-962D277B8B88}">
       <text>
         <r>
           <rPr>
@@ -114,7 +114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{63CC2A39-887A-4ED0-A3CF-879F00553721}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{63CC2A39-887A-4ED0-A3CF-879F00553721}">
       <text>
         <r>
           <rPr>
@@ -132,7 +132,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{7B08EDC2-9450-4D0E-BC3E-679B5C0F8CE2}">
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{7B08EDC2-9450-4D0E-BC3E-679B5C0F8CE2}">
       <text>
         <r>
           <rPr>
@@ -147,7 +147,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{FABC9E6E-5273-4913-8085-012620829B29}">
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{FABC9E6E-5273-4913-8085-012620829B29}">
       <text>
         <r>
           <rPr>
@@ -162,7 +162,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{C8160E2B-76BE-4EC9-B84F-541AF26D2261}">
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{C8160E2B-76BE-4EC9-B84F-541AF26D2261}">
       <text>
         <r>
           <rPr>
@@ -192,9 +192,6 @@
     <t>Ojeda, Paula</t>
   </si>
   <si>
-    <t>Fechas</t>
-  </si>
-  <si>
     <t>Última revisión:</t>
   </si>
   <si>
@@ -271,6 +268,9 @@
   </si>
   <si>
     <t>Gallucio, Tomas</t>
+  </si>
+  <si>
+    <t>Fechas / entregas</t>
   </si>
 </sst>
 </file>
@@ -512,11 +512,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -540,13 +539,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -567,11 +567,58 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -868,7 +915,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N27"/>
+  <dimension ref="B2:N28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
@@ -876,7 +923,7 @@
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H2" s="23" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
@@ -884,540 +931,657 @@
     </row>
     <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="21">
         <v>45942.525694444441</v>
       </c>
       <c r="E3" s="22"/>
-      <c r="H3" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="14"/>
+      <c r="H3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="12"/>
+      <c r="K3" s="13"/>
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="17" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="27"/>
+    </row>
+    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="19"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="17">
+        <v>1</v>
+      </c>
+      <c r="E7" s="17">
         <v>2</v>
       </c>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="20"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8">
+      <c r="F7" s="17">
+        <v>3</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17">
+        <v>4</v>
+      </c>
+      <c r="I7" s="17">
+        <v>5</v>
+      </c>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="17"/>
+      <c r="N7" s="28"/>
+    </row>
+    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="20"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="7">
         <v>45894</v>
       </c>
-      <c r="E7" s="8">
-        <f t="shared" ref="E7:K7" si="0">+D7+7</f>
+      <c r="E8" s="7">
+        <f t="shared" ref="E8:N8" si="0">+D8+7</f>
         <v>45901</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F8" s="7">
         <f t="shared" si="0"/>
         <v>45908</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G8" s="7">
         <f t="shared" si="0"/>
         <v>45915</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H8" s="7">
         <f t="shared" si="0"/>
         <v>45922</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I8" s="7">
         <f t="shared" si="0"/>
         <v>45929</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J8" s="7">
         <f t="shared" si="0"/>
         <v>45936</v>
       </c>
-      <c r="K7" s="9">
+      <c r="K8" s="7">
         <f t="shared" si="0"/>
         <v>45943</v>
       </c>
-    </row>
-    <row r="8" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6" t="s">
+      <c r="L8" s="7">
+        <f t="shared" ref="L8" si="1">+K8+7</f>
+        <v>45950</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" ref="M8" si="2">+L8+7</f>
+        <v>45957</v>
+      </c>
+      <c r="N8" s="8">
+        <f t="shared" si="0"/>
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="9"/>
+      <c r="K9" s="9"/>
+      <c r="L9" s="9"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="4"/>
+      <c r="D10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J10" s="9"/>
+      <c r="K10" s="9"/>
+      <c r="L10" s="9"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4"/>
+      <c r="D11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="15"/>
+      <c r="H11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
+      <c r="L11" s="9"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="10" t="s">
+      <c r="I12" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="10"/>
+    </row>
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="9"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="J8" s="10"/>
-      <c r="K8" s="11"/>
-    </row>
-    <row r="9" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="C14" s="4"/>
+      <c r="D14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="15"/>
+      <c r="H14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="9"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="10"/>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="10"/>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="10"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="15"/>
+      <c r="H17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="10"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="15"/>
+      <c r="H18" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
+      <c r="L18" s="9"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="10"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="15"/>
+      <c r="H19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+      <c r="L19" s="9"/>
+      <c r="M19" s="9"/>
+      <c r="N19" s="10"/>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="15"/>
+      <c r="H20" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+      <c r="K20" s="9"/>
+      <c r="L20" s="9"/>
+      <c r="M20" s="9"/>
+      <c r="N20" s="10"/>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
+      <c r="M21" s="9"/>
+      <c r="N21" s="10"/>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="15"/>
+      <c r="H22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9"/>
+      <c r="N22" s="10"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+      <c r="M23" s="9"/>
+      <c r="N23" s="10"/>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J9" s="10"/>
-      <c r="K9" s="11"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="11"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J11" s="10"/>
-      <c r="K11" s="11"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="11"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B13" s="6" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="15"/>
+      <c r="H24" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+      <c r="M24" s="9"/>
+      <c r="N24" s="10"/>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="11"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="11"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B15" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="11"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B16" s="6" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" s="15"/>
+      <c r="H25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+      <c r="M25" s="9"/>
+      <c r="N25" s="10"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J16" s="10"/>
-      <c r="K16" s="11"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="11"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="11"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="11"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="6" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="15"/>
+      <c r="H26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+      <c r="M26" s="9"/>
+      <c r="N26" s="10"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="16"/>
-      <c r="H20" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="11"/>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="11"/>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="11"/>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="6" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="15"/>
+      <c r="H27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+      <c r="M27" s="9"/>
+      <c r="N27" s="10"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="11"/>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="11"/>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="11"/>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="11"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="15"/>
+      <c r="H28" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+      <c r="M28" s="9"/>
+      <c r="N28" s="10"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B8:K27">
-    <sortCondition ref="B8:B27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:K28">
+    <sortCondition ref="B9:B28"/>
   </sortState>
   <mergeCells count="4">
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B6:B8"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
+    <mergeCell ref="D6:N6"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:K27">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="D9:J28">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N9:N28">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K9:K28">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L9:L28">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M9:M28">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISCO D\Francisco\Trabajos\FCE\Optativa\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F661FB-276D-4E08-9186-57195F1AB6C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11844E5E-5E90-444B-A905-24A2D26A821F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -54,6 +51,32 @@
           </rPr>
           <t>Error: objeto 'tab' no encontrado
 Error: objeto 'mean_by_month' no encontrado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{83B76502-D14F-4662-AE54-C8D42481514A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>&gt; p3_inter &lt;- ggplotly(p3, tooltip = "label")
+Error en rng[[xy]]$get_labels(): tentativa de aplicar una no-función
+Además: Avisos:
+1: In min(z[["x"]]$dimension %()% z$x.range %||% z$x_range) :
+  ningún argumento finito para min; retornando Inf
+2: In max(z[["x"]]$dimension %()% z$x.range %||% z$x_range) :
+  ningun argumento finito para max; retornando -Inf
+3: In min(z[["y"]]$dimension %()% z$y.range %||% z$y_range) :
+  ningún argumento finito para min; retornando Inf
+4: In max(z[["y"]]$dimension %()% z$y.range %||% z$y_range) :
+  ningun argumento finito para max; retornando -Inf
+&gt; p3_inter
+Error: objeto 'p3_inter' no encontrado</t>
         </r>
       </text>
     </comment>
@@ -132,6 +155,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{54D00BC5-4CFA-4C7A-82D0-B8A12BA3A15C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+&gt; datos_wdi &lt;- read.csv("datos_wdi.csv") # Cargo mi base de datos
+Error en file(file, "rt"): no se puede abrir la conexión
+Además: Aviso:
+In file(file, "rt") :
+  no fue posible abrir el archivo 'datos_wdi.csv': No such file or directory</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="H22" authorId="0" shapeId="0" xr:uid="{7B08EDC2-9450-4D0E-BC3E-679B5C0F8CE2}">
       <text>
         <r>
@@ -144,6 +186,20 @@
           </rPr>
           <t>Error en drop_na(., Ozone, Temp): 
   no se pudo encontrar la función "drop_na"</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{413263D4-DD29-47D7-AB06-01EF61010E15}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Error con la entrega enviada, parece ser otro Nº de entrega.</t>
         </r>
       </text>
     </comment>
@@ -162,7 +218,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{C8160E2B-76BE-4EC9-B84F-541AF26D2261}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{96B6402A-D9AF-46D1-A7DC-5FEE2CA79E1B}">
       <text>
         <r>
           <rPr>
@@ -172,10 +228,34 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Error en file(file, "rt"): no se puede abrir la conexión
-Además: Aviso:
-In file(file, "rt") :
-  no fue posible abrir el archivo '…/Programacion en R/base.csv': No such file or directory</t>
+          <t>&gt; g3 &lt;- ggplot(tabla, aes(x = "", y = Freq, fill = factor(Month))) +
++   geom_bar(stat = "identity", width = 1) +
++   coord_polar(theta = "y") +
++   labs(
++     title = "Proporción de observaciones por Mes",
++     fill = "Mes"
++   ) +
++   theme_void()
+Error: objeto 'tabla' no encontrado
+&gt; ggplotly(g3)
+Error: objeto 'Freq' no encontrado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{B386A6A9-0E43-4783-9890-65DB365F7508}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+Error: `path` does not exist: ‘Lista_de_clientes_con_nombre_y_direccion’
+&gt; clientes &lt;- read_excel("C:/ruta/Lista-de-clientes-con-nombre-y-direccion.xls")
+Error: `path` does not exist: ‘C:/ruta/Lista-de-clientes-con-nombre-y-direccion.xls’</t>
         </r>
       </text>
     </comment>
@@ -184,7 +264,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -512,7 +592,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -539,10 +619,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -573,52 +650,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -922,22 +958,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="24"/>
     </row>
     <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="21">
-        <v>45942.525694444441</v>
-      </c>
-      <c r="E3" s="22"/>
+      <c r="D3" s="20">
+        <v>45943.378472222219</v>
+      </c>
+      <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
         <v>4</v>
       </c>
@@ -949,51 +985,51 @@
     </row>
     <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="27"/>
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25"/>
+      <c r="M6" s="25"/>
+      <c r="N6" s="26"/>
     </row>
     <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="17">
+      <c r="B7" s="18"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="9">
         <v>2</v>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="9">
         <v>3</v>
       </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17">
+      <c r="G7" s="9"/>
+      <c r="H7" s="9">
         <v>4</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="9">
         <v>5</v>
       </c>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="28"/>
+      <c r="J7" s="9"/>
+      <c r="K7" s="9"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="16"/>
     </row>
     <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
+      <c r="B8" s="19"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
         <v>45894</v>
@@ -1111,7 +1147,9 @@
       <c r="H11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="9"/>
+      <c r="I11" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="J11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
@@ -1188,7 +1226,9 @@
       <c r="H14" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I14" s="9"/>
+      <c r="I14" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
@@ -1236,7 +1276,9 @@
       <c r="H16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I16" s="9"/>
+      <c r="I16" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
@@ -1313,7 +1355,9 @@
       <c r="H19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I19" s="9"/>
+      <c r="I19" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
@@ -1338,7 +1382,9 @@
       <c r="H20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I20" s="9"/>
+      <c r="I20" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="J20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
@@ -1363,7 +1409,9 @@
       <c r="H21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I21" s="9"/>
+      <c r="I21" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
@@ -1388,7 +1436,9 @@
       <c r="H22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I22" s="9"/>
+      <c r="I22" s="14" t="s">
+        <v>4</v>
+      </c>
       <c r="J22" s="9"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
@@ -1413,7 +1463,9 @@
       <c r="H23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I23" s="9"/>
+      <c r="I23" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="J23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
@@ -1463,7 +1515,9 @@
       <c r="H25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I25" s="9"/>
+      <c r="I25" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="J25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
@@ -1488,7 +1542,9 @@
       <c r="H26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I26" s="9"/>
+      <c r="I26" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="J26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
@@ -1513,7 +1569,9 @@
       <c r="H27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I27" s="9"/>
+      <c r="I27" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
@@ -1536,7 +1594,7 @@
       </c>
       <c r="G28" s="15"/>
       <c r="H28" s="14" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
@@ -1555,33 +1613,13 @@
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="D6:N6"/>
   </mergeCells>
-  <conditionalFormatting sqref="D9:J28">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+  <conditionalFormatting sqref="D9:N28">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="4" priority="23" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N9:N28">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K9:K28">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L9:L28">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"R"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M9:M28">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DISCO D\Francisco\Trabajos\FCE\Optativa\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11844E5E-5E90-444B-A905-24A2D26A821F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A78415-C0D0-4E65-8B9A-46398BDD199D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -80,34 +80,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{BAC2716D-1FF6-4460-89A0-0563EA2A9792}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Error: `path` does not exist: ‘Growth.xlsx’</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{452042C0-E791-466A-BF82-179BD80140AB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Error: `path` does not exist: ‘Growth.xlsx’</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="F13" authorId="0" shapeId="0" xr:uid="{3254A794-DC4A-404E-831A-F9197FDD3E71}">
       <text>
         <r>
@@ -119,21 +91,6 @@
             <family val="2"/>
           </rPr>
           <t>No corrió bien el codigo</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{CEEDE685-C6D5-416F-82DE-962D277B8B88}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-Error: objeto 'ventas_autos_caba' no encontrado</t>
         </r>
       </text>
     </comment>
@@ -156,6 +113,25 @@
       </text>
     </comment>
     <comment ref="I20" authorId="0" shapeId="0" xr:uid="{54D00BC5-4CFA-4C7A-82D0-B8A12BA3A15C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+&gt; datos_wdi &lt;- read.csv("datos_wdi.csv") # Cargo mi base de datos
+Error en file(file, "rt"): no se puede abrir la conexión
+Además: Aviso:
+In file(file, "rt") :
+  no fue posible abrir el archivo 'datos_wdi.csv': No such file or directory</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{AD638E5F-F377-4990-A421-8B88BEA4915C}">
       <text>
         <r>
           <rPr>
@@ -218,6 +194,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{33B50290-8D37-4F06-96A2-21AC55948CD4}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+Error: `path` does not exist: ‘encuesta_poblacional.xlsx’</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J24" authorId="0" shapeId="0" xr:uid="{C660C20F-CB5E-4C04-8846-FC5D4594AB5A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
+Error: `path` does not exist: ‘encuesta_poblacional.xlsx’</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="I25" authorId="0" shapeId="0" xr:uid="{96B6402A-D9AF-46D1-A7DC-5FEE2CA79E1B}">
       <text>
         <r>
@@ -242,29 +248,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{B386A6A9-0E43-4783-9890-65DB365F7508}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-Error: `path` does not exist: ‘Lista_de_clientes_con_nombre_y_direccion’
-&gt; clientes &lt;- read_excel("C:/ruta/Lista-de-clientes-con-nombre-y-direccion.xls")
-Error: `path` does not exist: ‘C:/ruta/Lista-de-clientes-con-nombre-y-direccion.xls’</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -654,7 +643,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -952,12 +951,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
@@ -965,13 +964,13 @@
       <c r="J2" s="23"/>
       <c r="K2" s="24"/>
     </row>
-    <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45943.378472222219</v>
+        <v>45949.817361111112</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -983,8 +982,8 @@
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +1002,7 @@
       <c r="M6" s="25"/>
       <c r="N6" s="26"/>
     </row>
-    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="18"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
@@ -1028,7 +1027,7 @@
       <c r="M7" s="9"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B8" s="19"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
@@ -1075,7 +1074,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1102,7 +1101,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1123,13 +1122,15 @@
       <c r="I10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="9"/>
+      <c r="J10" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1156,7 +1157,7 @@
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -1172,18 +1173,20 @@
       </c>
       <c r="G12" s="15"/>
       <c r="H12" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J12" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
@@ -1208,7 +1211,7 @@
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1229,13 +1232,15 @@
       <c r="I14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="9"/>
+      <c r="J14" s="14" t="s">
+        <v>26</v>
+      </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1258,7 +1263,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1285,7 +1290,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
@@ -1306,13 +1311,15 @@
       <c r="I17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="9"/>
+      <c r="J17" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1328,16 +1335,18 @@
       </c>
       <c r="G18" s="15"/>
       <c r="H18" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="I18" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1358,13 +1367,15 @@
       <c r="I19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="9"/>
+      <c r="J19" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1385,13 +1396,15 @@
       <c r="I20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="J20" s="9"/>
+      <c r="J20" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1412,13 +1425,15 @@
       <c r="I21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="9"/>
+      <c r="J21" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1445,7 +1460,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1466,13 +1481,15 @@
       <c r="I23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="9"/>
+      <c r="J23" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1490,14 +1507,18 @@
       <c r="H24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="I24" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1524,7 +1545,7 @@
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1543,15 +1564,17 @@
         <v>12</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J26" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
@@ -1578,7 +1601,7 @@
       <c r="M27" s="9"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
@@ -1614,12 +1637,12 @@
     <mergeCell ref="D6:N6"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:N28">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A78415-C0D0-4E65-8B9A-46398BDD199D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0D12FA-F5EF-48CA-AA83-9EDB4B0BECDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3840" yWindow="3840" windowWidth="12075" windowHeight="9585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -80,6 +83,21 @@
         </r>
       </text>
     </comment>
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{732E58AD-62D5-45A9-AB95-29428AF3A087}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Falta enviar base de datos
+</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F13" authorId="0" shapeId="0" xr:uid="{3254A794-DC4A-404E-831A-F9197FDD3E71}">
       <text>
         <r>
@@ -91,62 +109,6 @@
             <family val="2"/>
           </rPr>
           <t>No corrió bien el codigo</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{63CC2A39-887A-4ED0-A3CF-879F00553721}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-Error en file(file, "rt"): no se puede abrir la conexión
-Además: Aviso:
-In file(file, "rt") :
-  no fue posible abrir el archivo 'datos_wdi.csv': No such file or directory</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{54D00BC5-4CFA-4C7A-82D0-B8A12BA3A15C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-&gt; datos_wdi &lt;- read.csv("datos_wdi.csv") # Cargo mi base de datos
-Error en file(file, "rt"): no se puede abrir la conexión
-Además: Aviso:
-In file(file, "rt") :
-  no fue posible abrir el archivo 'datos_wdi.csv': No such file or directory</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{AD638E5F-F377-4990-A421-8B88BEA4915C}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-&gt; datos_wdi &lt;- read.csv("datos_wdi.csv") # Cargo mi base de datos
-Error en file(file, "rt"): no se puede abrir la conexión
-Además: Aviso:
-In file(file, "rt") :
-  no fue posible abrir el archivo 'datos_wdi.csv': No such file or directory</t>
         </r>
       </text>
     </comment>
@@ -248,12 +210,27 @@
         </r>
       </text>
     </comment>
+    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{D573ADB5-B073-425E-BEB7-C9A1B7C9BB50}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Falta enviar base de datos
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -643,17 +620,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -951,12 +918,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
@@ -964,13 +931,13 @@
       <c r="J2" s="23"/>
       <c r="K2" s="24"/>
     </row>
-    <row r="3" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45949.817361111112</v>
+        <v>45950.029861111114</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -982,8 +949,8 @@
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
@@ -1002,7 +969,7 @@
       <c r="M6" s="25"/>
       <c r="N6" s="26"/>
     </row>
-    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
@@ -1027,7 +994,7 @@
       <c r="M7" s="9"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="19"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
@@ -1074,7 +1041,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15" thickTop="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1101,7 +1068,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1130,7 +1097,7 @@
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1151,13 +1118,15 @@
       <c r="I11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="9"/>
+      <c r="J11" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -1186,7 +1155,7 @@
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
@@ -1211,7 +1180,7 @@
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1240,7 +1209,7 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1263,7 +1232,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1290,7 +1259,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
@@ -1319,7 +1288,7 @@
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1346,7 +1315,7 @@
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1375,7 +1344,7 @@
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1391,20 +1360,20 @@
       </c>
       <c r="G20" s="15"/>
       <c r="H20" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1433,7 +1402,7 @@
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1460,7 +1429,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1489,7 +1458,7 @@
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1518,7 +1487,7 @@
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1539,13 +1508,15 @@
       <c r="I25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J25" s="9"/>
+      <c r="J25" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1574,7 +1545,7 @@
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
@@ -1601,7 +1572,7 @@
       <c r="M27" s="9"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
@@ -1637,12 +1608,12 @@
     <mergeCell ref="D6:N6"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:N28">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="1" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD0D12FA-F5EF-48CA-AA83-9EDB4B0BECDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6AB190-328D-47D1-9D14-3DB5FF7CA5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="12075" windowHeight="9585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -83,7 +80,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{732E58AD-62D5-45A9-AB95-29428AF3A087}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{732E58AD-62D5-45A9-AB95-29428AF3A087}">
       <text>
         <r>
           <rPr>
@@ -141,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{FABC9E6E-5273-4913-8085-012620829B29}">
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{429BE6B8-851B-49BB-B40B-30EF9FF9EDED}">
       <text>
         <r>
           <rPr>
@@ -151,12 +148,21 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-Error: `path` does not exist: ‘encuesta_poblacional.xlsx’</t>
+          <t>&gt; g3 &lt;- ggplot(tabla, aes(x = "", y = Freq, fill = factor(Month))) +
++   geom_bar(stat = "identity", width = 1) +
++   coord_polar(theta = "y") +
++   labs(
++     title = "Proporción de observaciones por Mes",
++     fill = "Mes"
++   ) +
++   theme_void()
+Error: objeto 'tabla' no encontrado
+&gt; ggplotly(g3)
+Error: objeto 'Freq' no encontrado</t>
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{33B50290-8D37-4F06-96A2-21AC55948CD4}">
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{BAC1A85C-9A41-494E-AED5-8B137ABE4520}">
       <text>
         <r>
           <rPr>
@@ -166,23 +172,17 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-Error: `path` does not exist: ‘encuesta_poblacional.xlsx’</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J24" authorId="0" shapeId="0" xr:uid="{C660C20F-CB5E-4C04-8846-FC5D4594AB5A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>No pude corregir por falta de base de datos. Recomiendo enviar la msima para que pueda corregir el código
-Error: `path` does not exist: ‘encuesta_poblacional.xlsx’</t>
+          <t>&gt; g3 &lt;- ggplot(tabla, aes(x = "", y = Freq, fill = factor(Month))) +
++   geom_bar(stat = "identity", width = 1) +
++   coord_polar(theta = "y") +
++   labs(
++     title = "Proporción de observaciones por Mes",
++     fill = "Mes"
++   ) +
++   theme_void()
+Error: objeto 'tabla' no encontrado
+&gt; ggplotly(g3)
+Error: objeto 'Freq' no encontrado</t>
         </r>
       </text>
     </comment>
@@ -210,27 +210,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{D573ADB5-B073-425E-BEB7-C9A1B7C9BB50}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Falta enviar base de datos
-</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -937,7 +922,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45950.029861111114</v>
+        <v>45952.691666666666</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -989,8 +974,12 @@
         <v>5</v>
       </c>
       <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
+      <c r="K7" s="9">
+        <v>6</v>
+      </c>
+      <c r="L7" s="9">
+        <v>7</v>
+      </c>
       <c r="M7" s="9"/>
       <c r="N7" s="16"/>
     </row>
@@ -1062,8 +1051,10 @@
       <c r="I9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
@@ -1089,10 +1080,10 @@
       <c r="I10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K10" s="9"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
@@ -1118,10 +1109,10 @@
       <c r="I11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="9"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
@@ -1147,10 +1138,10 @@
       <c r="I12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="15"/>
+      <c r="K12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
@@ -1174,7 +1165,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="J13" s="15"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
@@ -1201,10 +1192,10 @@
       <c r="I14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="15"/>
+      <c r="K14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
@@ -1226,7 +1217,7 @@
       <c r="G15" s="15"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="J15" s="15"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -1253,7 +1244,7 @@
       <c r="I16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="9"/>
+      <c r="J16" s="15"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
@@ -1280,10 +1271,10 @@
       <c r="I17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="15"/>
+      <c r="K17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
@@ -1309,7 +1300,7 @@
       <c r="I18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="9"/>
+      <c r="J18" s="15"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
@@ -1336,10 +1327,10 @@
       <c r="I19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="9"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
@@ -1365,10 +1356,10 @@
       <c r="I20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K20" s="9"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
@@ -1394,10 +1385,10 @@
       <c r="I21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="K21" s="9"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
@@ -1423,7 +1414,7 @@
       <c r="I22" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="9"/>
+      <c r="J22" s="15"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
@@ -1450,10 +1441,10 @@
       <c r="I23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="K23" s="9"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
@@ -1474,15 +1465,15 @@
       </c>
       <c r="G24" s="15"/>
       <c r="H24" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K24" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="J24" s="15"/>
+      <c r="K24" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
@@ -1508,10 +1499,10 @@
       <c r="I25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J25" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K25" s="9"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
@@ -1537,10 +1528,10 @@
       <c r="I26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K26" s="9"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
@@ -1566,8 +1557,10 @@
       <c r="I27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="10"/>
@@ -1591,7 +1584,7 @@
         <v>11</v>
       </c>
       <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="J28" s="15"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE6AB190-328D-47D1-9D14-3DB5FF7CA5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F872C7DB-0DD4-403D-9DD1-E7097A52221A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -1055,7 +1055,9 @@
       <c r="K9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L9" s="9"/>
+      <c r="L9" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
     </row>
@@ -1084,7 +1086,9 @@
       <c r="K10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L10" s="9"/>
+      <c r="L10" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
     </row>
@@ -1113,7 +1117,9 @@
       <c r="K11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L11" s="9"/>
+      <c r="L11" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
     </row>
@@ -1142,7 +1148,9 @@
       <c r="K12" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="9"/>
+      <c r="L12" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
     </row>
@@ -1196,7 +1204,9 @@
       <c r="K14" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="L14" s="9"/>
+      <c r="L14" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
     </row>
@@ -1275,7 +1285,9 @@
       <c r="K17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L17" s="9"/>
+      <c r="L17" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
     </row>
@@ -1331,7 +1343,9 @@
       <c r="K19" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L19" s="9"/>
+      <c r="L19" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
     </row>
@@ -1360,7 +1374,9 @@
       <c r="K20" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L20" s="9"/>
+      <c r="L20" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
     </row>
@@ -1389,7 +1405,9 @@
       <c r="K21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L21" s="9"/>
+      <c r="L21" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
     </row>
@@ -1415,8 +1433,12 @@
         <v>4</v>
       </c>
       <c r="J22" s="15"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
+      <c r="K22" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
@@ -1561,7 +1583,9 @@
       <c r="K27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="L27" s="9"/>
+      <c r="L27" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="M27" s="9"/>
       <c r="N27" s="10"/>
     </row>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F872C7DB-0DD4-403D-9DD1-E7097A52221A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAD5D05-F600-4F0C-B0CA-2517199B34EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -95,6 +95,35 @@
         </r>
       </text>
     </comment>
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{C3304D79-866C-49AF-B0D8-22F45C937B79}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Fallo el código:
+&gt; stopifnot(length(anios_disp) &gt; 0)  # si falla, la lectura/pivoteo no encontró años
+Error: length(anios_disp) &gt; 0 is not TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{AE1C352F-378E-4B23-8CC9-32F8C2C8966E}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Falló el RMD</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F13" authorId="0" shapeId="0" xr:uid="{3254A794-DC4A-404E-831A-F9197FDD3E71}">
       <text>
         <r>
@@ -106,6 +135,21 @@
             <family val="2"/>
           </rPr>
           <t>No corrió bien el codigo</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0" xr:uid="{C01F821D-266A-4607-A166-0C1DBB03F325}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">En el archivo _1, faltaba cargar un paquete para usar la función ne_state en chunk de línea 135, y otros chunks (antepenúltimo y último). Se pudieron correr luego de correrlos.
+</t>
         </r>
       </text>
     </comment>
@@ -210,12 +254,26 @@
         </r>
       </text>
     </comment>
+    <comment ref="L26" authorId="0" shapeId="0" xr:uid="{269803E2-4E04-4DA6-8BCF-E9DC16159EA6}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Faltó elaboración de dashboard</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -308,7 +366,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,6 +388,19 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -543,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -599,6 +670,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -903,12 +977,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
@@ -916,13 +990,13 @@
       <c r="J2" s="23"/>
       <c r="K2" s="24"/>
     </row>
-    <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45952.691666666666</v>
+        <v>45958.944687499999</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -934,8 +1008,8 @@
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
@@ -954,7 +1028,7 @@
       <c r="M6" s="25"/>
       <c r="N6" s="26"/>
     </row>
-    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="18"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
@@ -983,7 +1057,7 @@
       <c r="M7" s="9"/>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="B8" s="19"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
@@ -1030,7 +1104,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1056,12 +1130,12 @@
         <v>11</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1087,12 +1161,12 @@
         <v>12</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M10" s="9"/>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1118,12 +1192,12 @@
         <v>12</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -1149,12 +1223,12 @@
         <v>26</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
@@ -1172,14 +1246,16 @@
       <c r="H13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="9"/>
+      <c r="I13" s="14" t="s">
+        <v>12</v>
+      </c>
       <c r="J13" s="15"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1205,12 +1281,12 @@
         <v>26</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1233,7 +1309,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1260,7 +1336,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
@@ -1286,12 +1362,12 @@
         <v>26</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="M17" s="9"/>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1318,7 +1394,7 @@
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1344,12 +1420,12 @@
         <v>11</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M19" s="9"/>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1375,12 +1451,12 @@
         <v>11</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1411,7 +1487,7 @@
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1442,7 +1518,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1471,7 +1547,7 @@
       <c r="M23" s="9"/>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1500,7 +1576,7 @@
       <c r="M24" s="9"/>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1529,7 +1605,7 @@
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1554,11 +1630,13 @@
       <c r="K26" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L26" s="9"/>
+      <c r="L26" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
@@ -1584,12 +1662,12 @@
         <v>12</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="M27" s="9"/>
+        <v>12</v>
+      </c>
+      <c r="M27" s="27"/>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEAD5D05-F600-4F0C-B0CA-2517199B34EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE9CF59-02A0-4F6A-B449-F7088085AFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -614,7 +614,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -670,9 +670,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -996,7 +993,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45958.944687499999</v>
+        <v>45958.973854166667</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -1482,7 +1479,7 @@
         <v>12</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
@@ -1664,7 +1661,7 @@
       <c r="L27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="27"/>
+      <c r="M27" s="9"/>
       <c r="N27" s="10"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE9CF59-02A0-4F6A-B449-F7088085AFBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D7FD3B-3496-4744-A6F2-CE3FC1139E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -273,7 +273,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="29">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -974,12 +974,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:N28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
@@ -987,13 +987,13 @@
       <c r="J2" s="23"/>
       <c r="K2" s="24"/>
     </row>
-    <row r="3" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45958.973854166667</v>
+        <v>45965.700243055559</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -1005,8 +1005,8 @@
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1025,7 @@
       <c r="M6" s="25"/>
       <c r="N6" s="26"/>
     </row>
-    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
@@ -1051,10 +1051,12 @@
       <c r="L7" s="9">
         <v>7</v>
       </c>
-      <c r="M7" s="9"/>
+      <c r="M7" s="9">
+        <v>8</v>
+      </c>
       <c r="N7" s="16"/>
     </row>
-    <row r="8" spans="2:14" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="19"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
@@ -1101,7 +1103,7 @@
         <v>45964</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1132,7 +1134,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="10"/>
     </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1160,10 +1162,12 @@
       <c r="L10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M10" s="9"/>
+      <c r="M10" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N10" s="10"/>
     </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1194,7 +1198,7 @@
       <c r="M11" s="9"/>
       <c r="N11" s="10"/>
     </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -1225,7 +1229,7 @@
       <c r="M12" s="9"/>
       <c r="N12" s="10"/>
     </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
@@ -1252,7 +1256,7 @@
       <c r="M13" s="9"/>
       <c r="N13" s="10"/>
     </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1283,7 +1287,7 @@
       <c r="M14" s="9"/>
       <c r="N14" s="10"/>
     </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1306,7 +1310,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="10"/>
     </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1333,7 +1337,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="10"/>
     </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
@@ -1361,10 +1365,12 @@
       <c r="L17" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="M17" s="9"/>
+      <c r="M17" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N17" s="10"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1391,7 +1397,7 @@
       <c r="M18" s="9"/>
       <c r="N18" s="10"/>
     </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1419,10 +1425,12 @@
       <c r="L19" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M19" s="9"/>
+      <c r="M19" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N19" s="10"/>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1453,7 +1461,7 @@
       <c r="M20" s="9"/>
       <c r="N20" s="10"/>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1484,7 +1492,7 @@
       <c r="M21" s="9"/>
       <c r="N21" s="10"/>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1515,7 +1523,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="10"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1541,10 +1549,12 @@
         <v>12</v>
       </c>
       <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
+      <c r="M23" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N23" s="10"/>
     </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1570,10 +1580,12 @@
         <v>11</v>
       </c>
       <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
+      <c r="M24" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N24" s="10"/>
     </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1602,7 +1614,7 @@
       <c r="M25" s="9"/>
       <c r="N25" s="10"/>
     </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1633,7 +1645,7 @@
       <c r="M26" s="9"/>
       <c r="N26" s="10"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
@@ -1661,10 +1673,12 @@
       <c r="L27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N27" s="10"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3D7FD3B-3496-4744-A6F2-CE3FC1139E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C8BDA4-7918-4069-85E5-23ABF76E5F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -108,6 +111,20 @@
           <t>Fallo el código:
 &gt; stopifnot(length(anios_disp) &gt; 0)  # si falla, la lectura/pivoteo no encontró años
 Error: length(anios_disp) &gt; 0 is not TRUE</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{50036834-8C37-4A7B-AF52-C47B16D2509C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>No corrió correctamente</t>
         </r>
       </text>
     </comment>
@@ -273,7 +290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="31">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -360,6 +377,12 @@
   </si>
   <si>
     <t>Fechas / entregas</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -973,13 +996,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:N28"/>
+  <dimension ref="B2:Q28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="24.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H2" s="22" t="s">
         <v>7</v>
       </c>
@@ -987,13 +1011,13 @@
       <c r="J2" s="23"/>
       <c r="K2" s="24"/>
     </row>
-    <row r="3" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="20">
-        <v>45965.700243055559</v>
+        <v>45971.901979166665</v>
       </c>
       <c r="E3" s="21"/>
       <c r="H3" s="11" t="s">
@@ -1005,8 +1029,8 @@
       <c r="J3" s="12"/>
       <c r="K3" s="13"/>
     </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17" t="s">
         <v>0</v>
       </c>
@@ -1023,9 +1047,10 @@
       <c r="K6" s="25"/>
       <c r="L6" s="25"/>
       <c r="M6" s="25"/>
-      <c r="N6" s="26"/>
-    </row>
-    <row r="7" spans="2:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N6" s="25"/>
+      <c r="O6" s="26"/>
+    </row>
+    <row r="7" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="18"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
@@ -1054,16 +1079,17 @@
       <c r="M7" s="9">
         <v>8</v>
       </c>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N7" s="9"/>
+      <c r="O7" s="16"/>
+    </row>
+    <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="19"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
         <v>45894</v>
       </c>
       <c r="E8" s="7">
-        <f t="shared" ref="E8:N8" si="0">+D8+7</f>
+        <f t="shared" ref="E8:K8" si="0">+D8+7</f>
         <v>45901</v>
       </c>
       <c r="F8" s="7">
@@ -1091,19 +1117,22 @@
         <v>45943</v>
       </c>
       <c r="L8" s="7">
-        <f t="shared" ref="L8" si="1">+K8+7</f>
+        <f t="shared" ref="L8:O8" si="1">+K8+7</f>
         <v>45950</v>
       </c>
       <c r="M8" s="7">
-        <f t="shared" ref="M8" si="2">+L8+7</f>
+        <f t="shared" si="1"/>
         <v>45957</v>
       </c>
-      <c r="N8" s="8">
-        <f t="shared" si="0"/>
+      <c r="N8" s="7">
+        <f>+O8-7</f>
         <v>45964</v>
       </c>
-    </row>
-    <row r="9" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="O8" s="8">
+        <v>45971</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1132,9 +1161,14 @@
         <v>26</v>
       </c>
       <c r="M9" s="9"/>
-      <c r="N9" s="10"/>
-    </row>
-    <row r="10" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N9" s="9"/>
+      <c r="O9" s="10"/>
+      <c r="Q9" t="str">
+        <f>+IF(COUNTA(D9:O9)&gt;6,B9,"")</f>
+        <v>Bidal, Mateo</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1163,11 +1197,16 @@
         <v>11</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N10" s="10"/>
-    </row>
-    <row r="11" spans="2:14" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="N10" s="9"/>
+      <c r="O10" s="10"/>
+      <c r="Q10" t="str">
+        <f t="shared" ref="Q10:Q28" si="2">+IF(COUNTA(D10:O10)&gt;6,B10,"")</f>
+        <v>Bonahora, Leandro Nahuel</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1195,10 +1234,17 @@
       <c r="L11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="N11" s="9"/>
+      <c r="O11" s="10"/>
+      <c r="Q11" t="str">
+        <f t="shared" si="2"/>
+        <v>Bressan, Diane</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -1226,10 +1272,17 @@
       <c r="L12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N12" s="9"/>
+      <c r="O12" s="10"/>
+      <c r="Q12" t="str">
+        <f t="shared" si="2"/>
+        <v>Enrique, Matías</v>
+      </c>
+    </row>
+    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
@@ -1254,9 +1307,14 @@
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N13" s="9"/>
+      <c r="O13" s="10"/>
+      <c r="Q13" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1284,10 +1342,17 @@
       <c r="L14" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="9"/>
-      <c r="N14" s="10"/>
-    </row>
-    <row r="15" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="9"/>
+      <c r="O14" s="10"/>
+      <c r="Q14" t="str">
+        <f t="shared" si="2"/>
+        <v>Gonzalez, Araceli</v>
+      </c>
+    </row>
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1308,9 +1373,14 @@
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
-      <c r="N15" s="10"/>
-    </row>
-    <row r="16" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N15" s="9"/>
+      <c r="O15" s="10"/>
+      <c r="Q15" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1335,9 +1405,14 @@
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
-      <c r="N16" s="10"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N16" s="9"/>
+      <c r="O16" s="10"/>
+      <c r="Q16" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
@@ -1366,11 +1441,18 @@
         <v>26</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="N17" s="9"/>
+      <c r="O17" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="2"/>
+        <v>Marello, Franco</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1395,9 +1477,16 @@
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
-      <c r="N18" s="10"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="9"/>
+      <c r="O18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q18" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1426,11 +1515,16 @@
         <v>11</v>
       </c>
       <c r="M19" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N19" s="10"/>
-    </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="N19" s="9"/>
+      <c r="O19" s="10"/>
+      <c r="Q19" t="str">
+        <f>+IF(COUNTA(D19:O19)&gt;6,B19,"")</f>
+        <v>Ojeda, Paula</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1459,9 +1553,14 @@
         <v>26</v>
       </c>
       <c r="M20" s="9"/>
-      <c r="N20" s="10"/>
-    </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N20" s="9"/>
+      <c r="O20" s="10"/>
+      <c r="Q20" t="str">
+        <f t="shared" si="2"/>
+        <v>Orellana, Demian</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1489,10 +1588,17 @@
       <c r="L21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="10"/>
-    </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N21" s="9"/>
+      <c r="O21" s="10"/>
+      <c r="Q21" t="str">
+        <f t="shared" si="2"/>
+        <v>Pereyra, Franco Andrés</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1515,15 +1621,20 @@
       </c>
       <c r="J22" s="15"/>
       <c r="K22" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M22" s="9"/>
-      <c r="N22" s="10"/>
-    </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="9"/>
+      <c r="O22" s="10"/>
+      <c r="Q22" t="str">
+        <f t="shared" si="2"/>
+        <v>Pontelli, Lara</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1550,11 +1661,16 @@
       </c>
       <c r="L23" s="9"/>
       <c r="M23" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N23" s="10"/>
-    </row>
-    <row r="24" spans="2:14" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+      <c r="N23" s="9"/>
+      <c r="O23" s="10"/>
+      <c r="Q23" t="str">
+        <f t="shared" si="2"/>
+        <v>Ríos, Joaquín</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1579,13 +1695,20 @@
       <c r="K24" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="L24" s="9"/>
+      <c r="L24" s="9" t="s">
+        <v>26</v>
+      </c>
       <c r="M24" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="N24" s="10"/>
-    </row>
-    <row r="25" spans="2:14" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="N24" s="9"/>
+      <c r="O24" s="10"/>
+      <c r="Q24" t="str">
+        <f t="shared" si="2"/>
+        <v>Silvestri, Julian</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1611,10 +1734,21 @@
         <v>12</v>
       </c>
       <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="10"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="O25" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q25" t="str">
+        <f t="shared" si="2"/>
+        <v>Solis, Melina</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1642,10 +1776,17 @@
       <c r="L26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="10"/>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="M26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" s="9"/>
+      <c r="O26" s="10"/>
+      <c r="Q26" t="str">
+        <f t="shared" si="2"/>
+        <v>Spinetta, Eros</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
@@ -1676,9 +1817,14 @@
       <c r="M27" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="N27" s="10"/>
-    </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="N27" s="9"/>
+      <c r="O27" s="10"/>
+      <c r="Q27" t="str">
+        <f t="shared" si="2"/>
+        <v>Tisocco, Augusto</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
@@ -1701,7 +1847,12 @@
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
-      <c r="N28" s="10"/>
+      <c r="N28" s="9"/>
+      <c r="O28" s="10"/>
+      <c r="Q28" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:K28">
@@ -1711,9 +1862,9 @@
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
-    <mergeCell ref="D6:N6"/>
+    <mergeCell ref="D6:O6"/>
   </mergeCells>
-  <conditionalFormatting sqref="D9:N28">
+  <conditionalFormatting sqref="D9:O28">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"R"</formula>
     </cfRule>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C8BDA4-7918-4069-85E5-23ABF76E5F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180C2496-7B61-4AEF-AF3D-997B0BFD136A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -290,7 +290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="32">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Asiste</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1120,7 @@
         <v>45943</v>
       </c>
       <c r="L8" s="7">
-        <f t="shared" ref="L8:O8" si="1">+K8+7</f>
+        <f t="shared" ref="L8:M8" si="1">+K8+7</f>
         <v>45950</v>
       </c>
       <c r="M8" s="7">
@@ -1163,9 +1166,8 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="10"/>
-      <c r="Q9" t="str">
-        <f>+IF(COUNTA(D9:O9)&gt;6,B9,"")</f>
-        <v>Bidal, Mateo</v>
+      <c r="Q9" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
@@ -1201,9 +1203,8 @@
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="10"/>
-      <c r="Q10" t="str">
-        <f t="shared" ref="Q10:Q28" si="2">+IF(COUNTA(D10:O10)&gt;6,B10,"")</f>
-        <v>Bonahora, Leandro Nahuel</v>
+      <c r="Q10" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="2:17" x14ac:dyDescent="0.25">
@@ -1239,9 +1240,8 @@
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="10"/>
-      <c r="Q11" t="str">
-        <f t="shared" si="2"/>
-        <v>Bressan, Diane</v>
+      <c r="Q11" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="2:17" x14ac:dyDescent="0.25">
@@ -1277,10 +1277,6 @@
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="10"/>
-      <c r="Q12" t="str">
-        <f t="shared" si="2"/>
-        <v>Enrique, Matías</v>
-      </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -1309,10 +1305,6 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="10"/>
-      <c r="Q13" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
@@ -1347,10 +1339,6 @@
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="10"/>
-      <c r="Q14" t="str">
-        <f t="shared" si="2"/>
-        <v>Gonzalez, Araceli</v>
-      </c>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
@@ -1375,10 +1363,6 @@
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="10"/>
-      <c r="Q15" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
@@ -1407,10 +1391,6 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="10"/>
-      <c r="Q16" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
@@ -1446,10 +1426,6 @@
       <c r="N17" s="9"/>
       <c r="O17" s="10" t="s">
         <v>29</v>
-      </c>
-      <c r="Q17" t="str">
-        <f t="shared" si="2"/>
-        <v>Marello, Franco</v>
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
@@ -1481,10 +1457,6 @@
       <c r="O18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
@@ -1519,10 +1491,6 @@
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="10"/>
-      <c r="Q19" t="str">
-        <f>+IF(COUNTA(D19:O19)&gt;6,B19,"")</f>
-        <v>Ojeda, Paula</v>
-      </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -1555,9 +1523,8 @@
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="10"/>
-      <c r="Q20" t="str">
-        <f t="shared" si="2"/>
-        <v>Orellana, Demian</v>
+      <c r="Q20" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.25">
@@ -1593,9 +1560,8 @@
       </c>
       <c r="N21" s="9"/>
       <c r="O21" s="10"/>
-      <c r="Q21" t="str">
-        <f t="shared" si="2"/>
-        <v>Pereyra, Franco Andrés</v>
+      <c r="Q21" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.25">
@@ -1629,10 +1595,6 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="10"/>
-      <c r="Q22" t="str">
-        <f t="shared" si="2"/>
-        <v>Pontelli, Lara</v>
-      </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
@@ -1665,10 +1627,6 @@
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="10"/>
-      <c r="Q23" t="str">
-        <f t="shared" si="2"/>
-        <v>Ríos, Joaquín</v>
-      </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
@@ -1703,10 +1661,6 @@
       </c>
       <c r="N24" s="9"/>
       <c r="O24" s="10"/>
-      <c r="Q24" t="str">
-        <f t="shared" si="2"/>
-        <v>Silvestri, Julian</v>
-      </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
@@ -1743,9 +1697,8 @@
       <c r="O25" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q25" t="str">
-        <f t="shared" si="2"/>
-        <v>Solis, Melina</v>
+      <c r="Q25" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.25">
@@ -1781,10 +1734,6 @@
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="10"/>
-      <c r="Q26" t="str">
-        <f t="shared" si="2"/>
-        <v>Spinetta, Eros</v>
-      </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
@@ -1819,10 +1768,6 @@
       </c>
       <c r="N27" s="9"/>
       <c r="O27" s="10"/>
-      <c r="Q27" t="str">
-        <f t="shared" si="2"/>
-        <v>Tisocco, Augusto</v>
-      </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
@@ -1849,9 +1794,8 @@
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
       <c r="O28" s="10"/>
-      <c r="Q28" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="Q28" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180C2496-7B61-4AEF-AF3D-997B0BFD136A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEA5AB7-11F1-4A54-B18D-9BF3E8AB178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -122,7 +119,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>No corrió correctamente</t>
         </r>
@@ -135,7 +132,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Falló el RMD</t>
         </r>
@@ -279,7 +276,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Faltó elaboración de dashboard</t>
         </r>
@@ -290,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="33">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -386,13 +383,16 @@
   </si>
   <si>
     <t>Asiste</t>
+  </si>
+  <si>
+    <t>Defensa final</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -419,14 +419,7 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -449,7 +442,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -636,11 +629,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -668,6 +685,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -697,6 +715,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1007,22 +1031,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="25"/>
     </row>
     <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="20">
+      <c r="D3" s="21">
         <v>45971.901979166665</v>
       </c>
-      <c r="E3" s="21"/>
+      <c r="E3" s="22"/>
       <c r="H3" s="11" t="s">
         <v>4</v>
       </c>
@@ -1034,27 +1058,30 @@
     </row>
     <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="18" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26"/>
+      <c r="H6" s="26"/>
+      <c r="I6" s="26"/>
+      <c r="J6" s="26"/>
+      <c r="K6" s="26"/>
+      <c r="L6" s="26"/>
+      <c r="M6" s="26"/>
+      <c r="N6" s="26"/>
+      <c r="O6" s="27"/>
+      <c r="Q6" s="28" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="18"/>
+      <c r="B7" s="19"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
         <v>1</v>
@@ -1084,9 +1111,10 @@
       </c>
       <c r="N7" s="9"/>
       <c r="O7" s="16"/>
+      <c r="Q7" s="29"/>
     </row>
     <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="19"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
         <v>45894</v>
@@ -1134,6 +1162,7 @@
       <c r="O8" s="8">
         <v>45971</v>
       </c>
+      <c r="Q8" s="17"/>
     </row>
     <row r="9" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
@@ -1166,7 +1195,7 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="10"/>
-      <c r="Q9" t="s">
+      <c r="Q9" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1203,7 +1232,7 @@
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="10"/>
-      <c r="Q10" t="s">
+      <c r="Q10" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1240,7 +1269,7 @@
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="10"/>
-      <c r="Q11" t="s">
+      <c r="Q11" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1277,6 +1306,9 @@
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="10"/>
+      <c r="Q12" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
@@ -1305,6 +1337,7 @@
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
       <c r="O13" s="10"/>
+      <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
@@ -1339,6 +1372,7 @@
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="10"/>
+      <c r="Q14" s="17"/>
     </row>
     <row r="15" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
@@ -1363,6 +1397,7 @@
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="10"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
@@ -1391,6 +1426,7 @@
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="10"/>
+      <c r="Q16" s="17"/>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
@@ -1427,6 +1463,7 @@
       <c r="O17" s="10" t="s">
         <v>29</v>
       </c>
+      <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
@@ -1457,6 +1494,7 @@
       <c r="O18" s="10" t="s">
         <v>30</v>
       </c>
+      <c r="Q18" s="17"/>
     </row>
     <row r="19" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
@@ -1491,6 +1529,7 @@
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="10"/>
+      <c r="Q19" s="17"/>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -1523,7 +1562,7 @@
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="10"/>
-      <c r="Q20" t="s">
+      <c r="Q20" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1560,7 +1599,7 @@
       </c>
       <c r="N21" s="9"/>
       <c r="O21" s="10"/>
-      <c r="Q21" t="s">
+      <c r="Q21" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1595,6 +1634,7 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="10"/>
+      <c r="Q22" s="17"/>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
@@ -1627,6 +1667,7 @@
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="10"/>
+      <c r="Q23" s="17"/>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
@@ -1661,6 +1702,9 @@
       </c>
       <c r="N24" s="9"/>
       <c r="O24" s="10"/>
+      <c r="Q24" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
@@ -1697,7 +1741,7 @@
       <c r="O25" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="Q25" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1734,6 +1778,9 @@
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="10"/>
+      <c r="Q26" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
@@ -1768,6 +1815,9 @@
       </c>
       <c r="N27" s="9"/>
       <c r="O27" s="10"/>
+      <c r="Q27" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
@@ -1794,7 +1844,7 @@
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
       <c r="O28" s="10"/>
-      <c r="Q28" t="s">
+      <c r="Q28" s="17" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1802,11 +1852,12 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:K28">
     <sortCondition ref="B9:B28"/>
   </sortState>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
     <mergeCell ref="D6:O6"/>
+    <mergeCell ref="Q6:Q7"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:O28">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CEA5AB7-11F1-4A54-B18D-9BF3E8AB178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A132E27-185E-49A9-B1D5-8EE77B75AC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -287,7 +290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="33">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -1529,7 +1532,9 @@
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="10"/>
-      <c r="Q19" s="17"/>
+      <c r="Q19" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
@@ -1667,7 +1672,9 @@
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="10"/>
-      <c r="Q23" s="17"/>
+      <c r="Q23" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A132E27-185E-49A9-B1D5-8EE77B75AC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63774C85-FDDC-443F-9EED-E4C6BDDD1A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -290,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="33">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -1047,7 +1044,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="21">
-        <v>45971.901979166665</v>
+        <v>45975.387638888889</v>
       </c>
       <c r="E3" s="22"/>
       <c r="H3" s="11" t="s">
@@ -1335,12 +1332,20 @@
         <v>12</v>
       </c>
       <c r="J13" s="15"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
+      <c r="K13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>4</v>
+      </c>
       <c r="N13" s="9"/>
       <c r="O13" s="10"/>
-      <c r="Q13" s="17"/>
+      <c r="Q13" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="14" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63774C85-FDDC-443F-9EED-E4C6BDDD1A89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7A2F50-04A4-4466-9062-EAF627E56F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -287,7 +290,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="33">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -1044,7 +1047,7 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="21">
-        <v>45975.387638888889</v>
+        <v>45977.733472222222</v>
       </c>
       <c r="E3" s="22"/>
       <c r="H3" s="11" t="s">
@@ -1471,7 +1474,9 @@
       <c r="O17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q17" s="17"/>
+      <c r="Q17" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">

--- a/Listado de prácticas.xlsx
+++ b/Listado de prácticas.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Trabajos\Optativa-FCE\UNL-Programacion-en-R\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositorios\UNL-Programacion-en-R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7A2F50-04A4-4466-9062-EAF627E56F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7B00DAE-2983-4438-86C7-8D398E46015B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -290,7 +287,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="34">
   <si>
     <t>Alumnos:</t>
   </si>
@@ -389,6 +386,9 @@
   </si>
   <si>
     <t>Defensa final</t>
+  </si>
+  <si>
+    <t>TP final enviado</t>
   </si>
 </sst>
 </file>
@@ -425,7 +425,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -441,6 +441,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -660,7 +666,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -679,8 +685,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -689,6 +693,27 @@
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -719,17 +744,44 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -1026,65 +1078,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:Q28"/>
+  <dimension ref="B2:S28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.5703125" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.85546875" customWidth="1"/>
+    <col min="10" max="10" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H2" s="23" t="s">
+    <row r="2" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="H2" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="25"/>
-    </row>
-    <row r="3" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="30"/>
+    </row>
+    <row r="3" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="2"/>
-      <c r="D3" s="21">
+      <c r="D3" s="26">
         <v>45977.733472222222</v>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="27"/>
       <c r="H3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="12" t="s">
+      <c r="I3" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="12"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="5" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
+      <c r="J3" s="21"/>
+      <c r="K3" s="22"/>
+    </row>
+    <row r="5" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="26"/>
-      <c r="H6" s="26"/>
-      <c r="I6" s="26"/>
-      <c r="J6" s="26"/>
-      <c r="K6" s="26"/>
-      <c r="L6" s="26"/>
-      <c r="M6" s="26"/>
-      <c r="N6" s="26"/>
-      <c r="O6" s="27"/>
-      <c r="Q6" s="28" t="s">
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="32"/>
+      <c r="Q6" s="19" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="7" spans="2:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19"/>
+      <c r="S6" s="19" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="24"/>
       <c r="C7" s="4"/>
       <c r="D7" s="9">
         <v>1</v>
@@ -1113,11 +1175,12 @@
         <v>8</v>
       </c>
       <c r="N7" s="9"/>
-      <c r="O7" s="16"/>
-      <c r="Q7" s="29"/>
-    </row>
-    <row r="8" spans="2:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="20"/>
+      <c r="O7" s="14"/>
+      <c r="Q7" s="20"/>
+      <c r="S7" s="20"/>
+    </row>
+    <row r="8" spans="2:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="25"/>
       <c r="C8" s="6"/>
       <c r="D8" s="7">
         <v>45894</v>
@@ -1165,9 +1228,10 @@
       <c r="O8" s="8">
         <v>45971</v>
       </c>
-      <c r="Q8" s="17"/>
-    </row>
-    <row r="9" spans="2:17" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="Q8" s="15"/>
+      <c r="S8" s="15"/>
+    </row>
+    <row r="9" spans="2:19" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>3</v>
       </c>
@@ -1181,14 +1245,14 @@
       <c r="F9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="14" t="s">
+      <c r="G9" s="13"/>
+      <c r="H9" s="12" t="s">
         <v>12</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="J9" s="13"/>
       <c r="K9" s="9" t="s">
         <v>11</v>
       </c>
@@ -1198,11 +1262,15 @@
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
       <c r="O9" s="10"/>
-      <c r="Q9" s="17" t="s">
+      <c r="Q9" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R9" s="17"/>
+      <c r="S9" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>22</v>
       </c>
@@ -1216,14 +1284,14 @@
       <c r="F10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="15"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="J10" s="13"/>
       <c r="K10" s="9" t="s">
         <v>12</v>
       </c>
@@ -1235,11 +1303,15 @@
       </c>
       <c r="N10" s="9"/>
       <c r="O10" s="10"/>
-      <c r="Q10" s="17" t="s">
+      <c r="Q10" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R10" s="17"/>
+      <c r="S10" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
@@ -1253,14 +1325,14 @@
       <c r="F11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="15"/>
+      <c r="G11" s="13"/>
       <c r="H11" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I11" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="J11" s="13"/>
       <c r="K11" s="9" t="s">
         <v>12</v>
       </c>
@@ -1272,11 +1344,15 @@
       </c>
       <c r="N11" s="9"/>
       <c r="O11" s="10"/>
-      <c r="Q11" s="17" t="s">
+      <c r="Q11" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R11" s="17"/>
+      <c r="S11" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>5</v>
       </c>
@@ -1290,14 +1366,14 @@
       <c r="F12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="15"/>
+      <c r="G12" s="13"/>
       <c r="H12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="J12" s="13"/>
       <c r="K12" s="9" t="s">
         <v>26</v>
       </c>
@@ -1309,32 +1385,36 @@
       </c>
       <c r="N12" s="9"/>
       <c r="O12" s="10"/>
-      <c r="Q12" s="17" t="s">
+      <c r="Q12" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="13" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R12" s="17"/>
+      <c r="S12" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="D13" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="15"/>
+      <c r="D13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="13"/>
       <c r="H13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="15"/>
+      <c r="I13" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="13"/>
       <c r="K13" s="9" t="s">
         <v>4</v>
       </c>
@@ -1346,11 +1426,15 @@
       </c>
       <c r="N13" s="9"/>
       <c r="O13" s="10"/>
-      <c r="Q13" s="17" t="s">
+      <c r="Q13" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R13" s="17"/>
+      <c r="S13" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>13</v>
       </c>
@@ -1364,15 +1448,15 @@
       <c r="F14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="15"/>
+      <c r="G14" s="13"/>
       <c r="H14" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="15"/>
-      <c r="K14" s="14" t="s">
+      <c r="J14" s="13"/>
+      <c r="K14" s="12" t="s">
         <v>26</v>
       </c>
       <c r="L14" s="9" t="s">
@@ -1383,9 +1467,11 @@
       </c>
       <c r="N14" s="9"/>
       <c r="O14" s="10"/>
-      <c r="Q14" s="17"/>
-    </row>
-    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q14" s="16"/>
+      <c r="R14" s="17"/>
+      <c r="S14" s="33"/>
+    </row>
+    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
@@ -1399,18 +1485,20 @@
       <c r="F15" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="9"/>
       <c r="I15" s="9"/>
-      <c r="J15" s="15"/>
+      <c r="J15" s="13"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
       <c r="O15" s="10"/>
-      <c r="Q15" s="17"/>
-    </row>
-    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q15" s="16"/>
+      <c r="R15" s="17"/>
+      <c r="S15" s="33"/>
+    </row>
+    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
@@ -1421,25 +1509,27 @@
       <c r="E16" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F16" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="15"/>
+      <c r="F16" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="13"/>
       <c r="H16" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I16" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J16" s="15"/>
+      <c r="J16" s="13"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
       <c r="O16" s="10"/>
-      <c r="Q16" s="17"/>
-    </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q16" s="16"/>
+      <c r="R16" s="17"/>
+      <c r="S16" s="33"/>
+    </row>
+    <row r="17" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
@@ -1453,14 +1543,14 @@
       <c r="F17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="15"/>
+      <c r="G17" s="13"/>
       <c r="H17" s="9" t="s">
         <v>11</v>
       </c>
       <c r="I17" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J17" s="15"/>
+      <c r="J17" s="13"/>
       <c r="K17" s="9" t="s">
         <v>26</v>
       </c>
@@ -1474,11 +1564,15 @@
       <c r="O17" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q17" s="17" t="s">
+      <c r="Q17" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="17"/>
+      <c r="S17" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>6</v>
       </c>
@@ -1489,17 +1583,17 @@
       <c r="E18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="15"/>
+      <c r="F18" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="13"/>
       <c r="H18" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I18" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J18" s="15"/>
+      <c r="J18" s="13"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
@@ -1507,9 +1601,11 @@
       <c r="O18" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="Q18" s="17"/>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q18" s="16"/>
+      <c r="R18" s="17"/>
+      <c r="S18" s="33"/>
+    </row>
+    <row r="19" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>1</v>
       </c>
@@ -1523,14 +1619,14 @@
       <c r="F19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G19" s="15"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I19" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J19" s="15"/>
+      <c r="J19" s="13"/>
       <c r="K19" s="9" t="s">
         <v>11</v>
       </c>
@@ -1542,11 +1638,15 @@
       </c>
       <c r="N19" s="9"/>
       <c r="O19" s="10"/>
-      <c r="Q19" s="17" t="s">
+      <c r="Q19" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="17"/>
+      <c r="S19" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
@@ -1560,14 +1660,14 @@
       <c r="F20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G20" s="15"/>
+      <c r="G20" s="13"/>
       <c r="H20" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I20" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J20" s="15"/>
+      <c r="J20" s="13"/>
       <c r="K20" s="9" t="s">
         <v>11</v>
       </c>
@@ -1577,11 +1677,15 @@
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
       <c r="O20" s="10"/>
-      <c r="Q20" s="17" t="s">
+      <c r="Q20" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R20" s="17"/>
+      <c r="S20" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>18</v>
       </c>
@@ -1595,14 +1699,14 @@
       <c r="F21" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G21" s="15"/>
+      <c r="G21" s="13"/>
       <c r="H21" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I21" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="J21" s="15"/>
+      <c r="J21" s="13"/>
       <c r="K21" s="9" t="s">
         <v>12</v>
       </c>
@@ -1614,11 +1718,15 @@
       </c>
       <c r="N21" s="9"/>
       <c r="O21" s="10"/>
-      <c r="Q21" s="17" t="s">
+      <c r="Q21" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R21" s="17"/>
+      <c r="S21" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1632,14 +1740,14 @@
       <c r="F22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G22" s="15"/>
+      <c r="G22" s="13"/>
       <c r="H22" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="I22" s="14" t="s">
+      <c r="I22" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="15"/>
+      <c r="J22" s="13"/>
       <c r="K22" s="9" t="s">
         <v>12</v>
       </c>
@@ -1649,9 +1757,11 @@
       <c r="M22" s="9"/>
       <c r="N22" s="9"/>
       <c r="O22" s="10"/>
-      <c r="Q22" s="17"/>
-    </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="Q22" s="16"/>
+      <c r="R22" s="17"/>
+      <c r="S22" s="33"/>
+    </row>
+    <row r="23" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1665,15 +1775,15 @@
       <c r="F23" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="15"/>
+      <c r="G23" s="13"/>
       <c r="H23" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I23" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J23" s="15"/>
-      <c r="K23" s="14" t="s">
+      <c r="J23" s="13"/>
+      <c r="K23" s="12" t="s">
         <v>12</v>
       </c>
       <c r="L23" s="9"/>
@@ -1682,11 +1792,15 @@
       </c>
       <c r="N23" s="9"/>
       <c r="O23" s="10"/>
-      <c r="Q23" s="17" t="s">
+      <c r="Q23" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="17"/>
+      <c r="S23" s="18" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>23</v>
       </c>
@@ -1700,14 +1814,14 @@
       <c r="F24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G24" s="15"/>
+      <c r="G24" s="13"/>
       <c r="H24" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I24" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J24" s="15"/>
+      <c r="J24" s="13"/>
       <c r="K24" s="9" t="s">
         <v>11</v>
       </c>
@@ -1719,11 +1833,15 @@
       </c>
       <c r="N24" s="9"/>
       <c r="O24" s="10"/>
-      <c r="Q24" s="17" t="s">
+      <c r="Q24" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="17"/>
+      <c r="S24" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>14</v>
       </c>
@@ -1737,14 +1855,14 @@
       <c r="F25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G25" s="15"/>
+      <c r="G25" s="13"/>
       <c r="H25" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I25" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J25" s="15"/>
+      <c r="J25" s="13"/>
       <c r="K25" s="9" t="s">
         <v>12</v>
       </c>
@@ -1758,11 +1876,15 @@
       <c r="O25" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="Q25" s="17" t="s">
+      <c r="Q25" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="17"/>
+      <c r="S25" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
@@ -1776,14 +1898,14 @@
       <c r="F26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G26" s="15"/>
+      <c r="G26" s="13"/>
       <c r="H26" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I26" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J26" s="15"/>
+      <c r="J26" s="13"/>
       <c r="K26" s="9" t="s">
         <v>11</v>
       </c>
@@ -1795,11 +1917,15 @@
       </c>
       <c r="N26" s="9"/>
       <c r="O26" s="10"/>
-      <c r="Q26" s="17" t="s">
+      <c r="Q26" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R26" s="17"/>
+      <c r="S26" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="5" t="s">
         <v>19</v>
       </c>
@@ -1813,14 +1939,14 @@
       <c r="F27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="G27" s="15"/>
+      <c r="G27" s="13"/>
       <c r="H27" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I27" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J27" s="15"/>
+      <c r="J27" s="13"/>
       <c r="K27" s="9" t="s">
         <v>12</v>
       </c>
@@ -1832,11 +1958,15 @@
       </c>
       <c r="N27" s="9"/>
       <c r="O27" s="10"/>
-      <c r="Q27" s="17" t="s">
+      <c r="Q27" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="R27" s="17"/>
+      <c r="S27" s="16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
         <v>15</v>
       </c>
@@ -1847,29 +1977,35 @@
       <c r="E28" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="15"/>
-      <c r="H28" s="14" t="s">
+      <c r="F28" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="13"/>
+      <c r="H28" s="12" t="s">
         <v>11</v>
       </c>
       <c r="I28" s="9"/>
-      <c r="J28" s="15"/>
+      <c r="J28" s="13"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
       <c r="N28" s="9"/>
       <c r="O28" s="10"/>
-      <c r="Q28" s="17" t="s">
+      <c r="Q28" s="16" t="s">
         <v>31</v>
+      </c>
+      <c r="R28" s="17"/>
+      <c r="S28" s="16" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B9:K28">
     <sortCondition ref="B9:B28"/>
   </sortState>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="S6:S7"/>
+    <mergeCell ref="I3:K3"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="H2:K2"/>
@@ -1877,13 +2013,18 @@
     <mergeCell ref="Q6:Q7"/>
   </mergeCells>
   <conditionalFormatting sqref="D9:O28">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"R"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3">
-    <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="24" operator="equal">
       <formula>"R"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S9:S28">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>" "</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
